--- a/artfynd/A 13924-2026 artfynd.xlsx
+++ b/artfynd/A 13924-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,69 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>85476738</v>
+        <v>90194743</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vivstabergets SV-sluttning, 200 m NO om korsningen Fasanvägen-Frölandsvägen, Mpd</t>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>618463</v>
+        <v>618435</v>
       </c>
       <c r="R2" t="n">
-        <v>6930383</v>
+        <v>6930108</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,19 +750,24 @@
           <t>Timrå</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Y-Tim-0244</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-05-16</t>
+          <t>2021-01-12</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-05-16</t>
+          <t>2021-01-12</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,32 +776,4283 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Stenbunden sluttning i äldre barrblandskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>89736844</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100011</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsörn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Aquila chrysaetos</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-12-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-12-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Aktiv flykt mot sv.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100025308</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57879</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100034</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blå kärrhök</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Circus cyaneus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1766)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-04-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-04-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>90281805</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57966</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-01-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-01-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>115145539</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>85608676</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56845</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100053</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-05-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>23:14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-05-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>23:14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>85388918</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57986</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100054</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pilgrimsfalk</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Falco peregrinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Tunstall, 1771</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>95774740</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57602</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Smålom</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Gavia stellata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>115535295</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57258</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>93230620</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-05-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-05-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>86549227</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58067</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100090</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nötkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nucifraga caryocatactes</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2020-06-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2020-06-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>108435019</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57340</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100091</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Storspov</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Numenius arquata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-04-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-04-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133287548</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57847</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100096</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pandion haliaetus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>85729054</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57838</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100100</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bivråk</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pernis apivorus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-05-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-05-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>98735592</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100110</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-02-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-02-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>96625043</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102110</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fjällvråk</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Buteo lagopus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133389042</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57964</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>97006503</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58592</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-11-05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-11-05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>103525290</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57981</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>102611</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Stenfalk</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Falco columbarius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-09-12</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-09-12</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>106922120</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-02-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-02-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>115596067</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57317</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102952</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tofsvipa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Vanellus vanellus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>111479066</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57774</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>93285332</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58209</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102980</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ladusvala</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hirundo rustica</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-05-11</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-05-11</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>93232314</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58212</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>102981</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Hussvala</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Delichon urbicum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2021-05-09</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2021-05-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>100025383</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58541</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102987</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sädesärla</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Motacilla alba</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-04-18</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-04-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>92303601</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>98475410</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-02-05</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-02-05</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>91987385</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2021-03-30</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2021-03-30</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>93385757</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58286</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>85077208</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2020-05-03</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2020-05-03</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132024818</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58250</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103019</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Stjärtmes</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Aegithalos caudatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>114111197</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132107122</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>106624693</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-02-11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-02-11</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>93565453</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58586</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103051</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Rosenfink</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carpodacus erythrinus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Pallas, 1770)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2021-05-18</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2021-05-18</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>93874079</v>
+      </c>
+      <c r="B37" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Frölandsvägen 28,Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>618435</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6930108</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2021-05-29</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2021-05-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Staffan Bergman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>85476738</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Vivstabergets SV-sluttning, 200 m NO om korsningen Fasanvägen-Frölandsvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>618463</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6930383</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Y-Tim-0244</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2020-05-16</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2020-05-16</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Stenbunden sluttning i äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
           <t>Agneta Toomingas</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>Agneta Toomingas</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY38" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
